--- a/SkillUp_FE/public/quiz_questions_template.xlsx
+++ b/SkillUp_FE/public/quiz_questions_template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FPT codes\SEP\Online-Learning-Platform-SkillUp\SkillUp_FE\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B40096C3-6BF9-4A2C-B602-F5E34384FE47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C2E265C-1C42-4852-8F3E-A1BFD406F403}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1100" yWindow="1100" windowWidth="19200" windowHeight="9970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -46,9 +46,6 @@
     <t>Hướng Dẫn Sử Dụng</t>
   </si>
   <si>
-    <t>Thêm câu hỏi vào Cột A (Câu Hỏi)</t>
-  </si>
-  <si>
     <t>Đáp án A</t>
   </si>
   <si>
@@ -64,15 +61,6 @@
     <t>Đáp án D</t>
   </si>
   <si>
-    <t>Thêm lần lượt các đáp án (Tối đa 4) vào từng cột đáp án tương ứng</t>
-  </si>
-  <si>
-    <t>Ghi đáp án đúng vào cột Đáp án đúng</t>
-  </si>
-  <si>
-    <t>Có thể chọn nhiều đáp án đúng, nhưng giữa chúng phải được ngăn cách bằng dấu ,</t>
-  </si>
-  <si>
     <t>2 + 2 = ?</t>
   </si>
   <si>
@@ -82,9 +70,6 @@
     <t>Hãy chọn tất cả số chẵn.</t>
   </si>
   <si>
-    <t>B,C</t>
-  </si>
-  <si>
     <t>Đáp án E</t>
   </si>
   <si>
@@ -92,6 +77,146 @@
   </si>
   <si>
     <t>Đáp án G</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Thêm câu hỏi vào </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Cột A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (Câu Hỏi)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Thêm lần lượt các đáp án </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(Tối đa 7)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> vào </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>từng cột đáp án tương ứng</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Ghi đáp án </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>đúng</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> vào </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>cột I (Đáp án đúng)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Có thể chọn </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>nhiều đáp án đúng</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, nhưng giữa chúng </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>phải được ngăn cách bằng dấu phẩy (,)</t>
+    </r>
+  </si>
+  <si>
+    <t>B,D</t>
   </si>
 </sst>
 </file>
@@ -333,7 +458,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -356,12 +481,12 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
@@ -374,8 +499,23 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -682,7 +822,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R6"/>
+  <dimension ref="A1:R7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="26.26953125" style="3" customWidth="1"/>
@@ -696,12 +836,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="20"/>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
+      <c r="A1" s="8"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
       <c r="G1"/>
       <c r="H1"/>
       <c r="I1"/>
@@ -712,44 +852,44 @@
         <v>6</v>
       </c>
       <c r="B2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="G2" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="H2" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>10</v>
-      </c>
       <c r="J2"/>
-      <c r="K2" s="17" t="s">
+      <c r="K2" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="L2" s="18"/>
-      <c r="M2" s="18"/>
-      <c r="N2" s="18"/>
-      <c r="O2" s="18"/>
-      <c r="P2" s="18"/>
-      <c r="Q2" s="18"/>
-      <c r="R2" s="19"/>
+      <c r="L2" s="16"/>
+      <c r="M2" s="16"/>
+      <c r="N2" s="16"/>
+      <c r="O2" s="16"/>
+      <c r="P2" s="16"/>
+      <c r="Q2" s="16"/>
+      <c r="R2" s="17"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B3" s="1">
         <v>3</v>
@@ -767,20 +907,20 @@
         <v>4</v>
       </c>
       <c r="J3" s="2"/>
-      <c r="K3" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="L3" s="15"/>
-      <c r="M3" s="15"/>
-      <c r="N3" s="15"/>
-      <c r="O3" s="15"/>
-      <c r="P3" s="15"/>
-      <c r="Q3" s="15"/>
-      <c r="R3" s="16"/>
+      <c r="K3" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="L3" s="13"/>
+      <c r="M3" s="13"/>
+      <c r="N3" s="13"/>
+      <c r="O3" s="13"/>
+      <c r="P3" s="13"/>
+      <c r="Q3" s="13"/>
+      <c r="R3" s="14"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>0</v>
@@ -798,20 +938,20 @@
         <v>5</v>
       </c>
       <c r="J4" s="2"/>
-      <c r="K4" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="L4" s="9"/>
-      <c r="M4" s="9"/>
-      <c r="N4" s="9"/>
-      <c r="O4" s="9"/>
-      <c r="P4" s="9"/>
-      <c r="Q4" s="9"/>
-      <c r="R4" s="10"/>
+      <c r="K4" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L4" s="10"/>
+      <c r="M4" s="10"/>
+      <c r="N4" s="10"/>
+      <c r="O4" s="10"/>
+      <c r="P4" s="10"/>
+      <c r="Q4" s="10"/>
+      <c r="R4" s="11"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B5" s="1">
         <v>1</v>
@@ -826,38 +966,48 @@
         <v>4</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J5" s="2"/>
-      <c r="K5" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="L5" s="9"/>
-      <c r="M5" s="9"/>
-      <c r="N5" s="9"/>
-      <c r="O5" s="9"/>
-      <c r="P5" s="9"/>
-      <c r="Q5" s="9"/>
-      <c r="R5" s="10"/>
+      <c r="K5" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="L5" s="10"/>
+      <c r="M5" s="10"/>
+      <c r="N5" s="10"/>
+      <c r="O5" s="10"/>
+      <c r="P5" s="10"/>
+      <c r="Q5" s="10"/>
+      <c r="R5" s="11"/>
     </row>
-    <row r="6" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="J6" s="2"/>
-      <c r="K6" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="L6" s="12"/>
-      <c r="M6" s="12"/>
-      <c r="N6" s="12"/>
-      <c r="O6" s="12"/>
-      <c r="P6" s="12"/>
-      <c r="Q6" s="12"/>
-      <c r="R6" s="13"/>
+      <c r="K6" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="L6" s="19"/>
+      <c r="M6" s="19"/>
+      <c r="N6" s="19"/>
+      <c r="O6" s="19"/>
+      <c r="P6" s="19"/>
+      <c r="Q6" s="19"/>
+      <c r="R6" s="20"/>
+    </row>
+    <row r="7" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="K7" s="21"/>
+      <c r="L7" s="22"/>
+      <c r="M7" s="22"/>
+      <c r="N7" s="22"/>
+      <c r="O7" s="22"/>
+      <c r="P7" s="22"/>
+      <c r="Q7" s="22"/>
+      <c r="R7" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="K6:R7"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="K5:R5"/>
-    <mergeCell ref="K6:R6"/>
     <mergeCell ref="K4:R4"/>
     <mergeCell ref="K3:R3"/>
     <mergeCell ref="K2:R2"/>
